--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-23.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-23.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_2515919C545AB40CB3DA2911595ED87656CD9798" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD0DE0FE-218E-47B5-BDD3-AC9555789BC5}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_2515919C545AB40CB3DA2911595ED87656CD9798" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F553C9F-026E-4FA7-B05D-6B5A7BADD067}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
   <si>
     <t>Data</t>
   </si>
@@ -119,15 +119,6 @@
     <t>PSV x FC Groningen</t>
   </si>
   <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>SERBIA 2</t>
-  </si>
-  <si>
-    <t>FK Loznica x FK Bor 1919</t>
-  </si>
-  <si>
     <t>Lay Under 0.5 FT (Fav)</t>
   </si>
   <si>
@@ -158,12 +149,6 @@
     <t>14:00</t>
   </si>
   <si>
-    <t>EGYPT 1</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo x ENPPI</t>
-  </si>
-  <si>
     <t>SERBIA 1</t>
   </si>
   <si>
@@ -207,15 +192,6 @@
   </si>
   <si>
     <t>Nacional (Uru) x Progreso</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>COLOMBIA 1</t>
-  </si>
-  <si>
-    <t>Deportivo Cali x Internacional de Bogotá</t>
   </si>
   <si>
     <t>20:30</t>
@@ -320,10 +296,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
@@ -653,10 +625,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -739,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M17" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
+        <f t="shared" ref="M3:M14" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
         <v>0.19416498993963782</v>
       </c>
     </row>
@@ -832,41 +804,41 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>6.59</v>
       </c>
       <c r="I6">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0.17262969588550983</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -874,13 +846,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -895,7 +867,7 @@
         <v>6.59</v>
       </c>
       <c r="I7">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -916,7 +888,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -934,10 +906,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>6.59</v>
+        <v>7.83</v>
       </c>
       <c r="I8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -950,7 +922,7 @@
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>0.17262969588550983</v>
+        <v>0.14128843338213762</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -961,38 +933,38 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9">
-        <v>9.66</v>
+        <v>7.42</v>
       </c>
       <c r="I9">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.11143187066974596</v>
+        <v>0.15031152647975077</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1003,38 +975,38 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
         <v>43</v>
       </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10">
-        <v>7.83</v>
+        <v>14.18</v>
       </c>
       <c r="I10">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
-        <v>0.14128843338213762</v>
+        <v>7.3216995447647953E-2</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1042,10 +1014,10 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>46</v>
@@ -1060,10 +1032,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>7.42</v>
+        <v>6.59</v>
       </c>
       <c r="I11">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -1076,7 +1048,7 @@
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>0.15031152647975077</v>
+        <v>0.17262969588550983</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1084,41 +1056,41 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12">
-        <v>14.18</v>
+        <v>6.39</v>
       </c>
       <c r="I12">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
-        <v>7.3216995447647953E-2</v>
+        <v>0.1790352504638219</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1126,41 +1098,41 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="H13">
-        <v>6.59</v>
+        <v>14.7</v>
       </c>
       <c r="I13">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="M13">
         <f t="shared" si="0"/>
-        <v>0.17262969588550983</v>
+        <v>7.0437956204379565E-2</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1168,13 +1140,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -1186,10 +1158,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>6.39</v>
+        <v>6.59</v>
       </c>
       <c r="I14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -1201,132 +1173,6 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
-        <v>0.1790352504638219</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15">
-        <v>14.7</v>
-      </c>
-      <c r="I15">
-        <v>1.47</v>
-      </c>
-      <c r="J15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>7.0437956204379565E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>11.03</v>
-      </c>
-      <c r="I16">
-        <v>1.58</v>
-      </c>
-      <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>9.6211365902293122E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17">
-        <v>6.59</v>
-      </c>
-      <c r="I17">
-        <v>1.27</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
         <f t="shared" si="0"/>
         <v>0.17262969588550983</v>
       </c>
